--- a/outputs/168-17.xlsx
+++ b/outputs/168-17.xlsx
@@ -21,7 +21,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t xml:space="preserve">Sub DeletePrecedingRows()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim rng As Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Set rng = Columns("A").Find(What:="Invoice No.", LookIn:=xlValues, LookAt:=xlWhole)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    If Not rng Is Nothing Then</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Rows("1:" &amp; (rng.Row - 1)).Delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    End If</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Sub</t>
+  </si>
   <si>
     <t xml:space="preserve">Invoice No.</t>
   </si>
@@ -42,11 +63,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,6 +90,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
@@ -119,12 +148,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -317,28 +358,70 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A2:E12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -359,20 +442,20 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/168-17.xlsx
+++ b/outputs/168-17.xlsx
@@ -21,28 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t xml:space="preserve">Sub DeletePrecedingRows()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Dim rng As Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Set rng = Columns("A").Find(What:="Invoice No.", LookIn:=xlValues, LookAt:=xlWhole)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    If Not rng Is Nothing Then</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Rows("1:" &amp; (rng.Row - 1)).Delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    End If</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End Sub</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="5">
   <si>
     <t xml:space="preserve">Invoice No.</t>
   </si>
@@ -358,52 +337,53 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:E12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="A4" s="3"/>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="A5" s="3"/>
       <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="A8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="3"/>
@@ -416,11 +396,21 @@
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -443,19 +433,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
